--- a/tools/convert_excel_to_md_model.xlsx
+++ b/tools/convert_excel_to_md_model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/project/YingVickyCao.github.io/doc/tools/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/project/YingVickyCao.github.io/tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339024FE-F607-AC4A-9B89-C685EA591068}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328C6680-7484-2848-893E-08802E56636C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="17540" xr2:uid="{CE9A8E0E-7C5D-A34E-B819-2211D9A6DAA1}"/>
+    <workbookView xWindow="1440" yWindow="1420" windowWidth="11340" windowHeight="17540" xr2:uid="{CE9A8E0E-7C5D-A34E-B819-2211D9A6DAA1}"/>
   </bookViews>
   <sheets>
     <sheet name="xml" sheetId="3" r:id="rId1"/>
@@ -34,33 +34,232 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
   <si>
     <t>|</t>
   </si>
   <si>
-    <t>描述</t>
-  </si>
-  <si>
     <t>---</t>
   </si>
   <si>
     <t>https://blog.csdn.net/wolinghuanyun/article/details/52811009</t>
   </si>
   <si>
-    <t>常见XML 属性</t>
-  </si>
-  <si>
-    <t>提示文本</t>
-  </si>
-  <si>
-    <t>是否自动缩小为图标</t>
-  </si>
-  <si>
-    <t>android:queryHint</t>
-  </si>
-  <si>
-    <t>android:iconifiedByDefault</t>
+    <t>基本类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>大小(1个字节等于8位)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>-2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>= -128</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1 = 127</t>
+    </r>
+  </si>
+  <si>
+    <t>\u0000' = Unicode 0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>\uFFFF' = Unicode 2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线 (Body)"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线 (Body)"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>-2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+      </rPr>
+      <t>15</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线 (Body)"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>-2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+      </rPr>
+      <t>31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线 (Body)"/>
+      </rPr>
+      <t>31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>-2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+      </rPr>
+      <t>63</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+      </rPr>
+      <t>63</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
+  <si>
+    <t>IEEE754</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -68,7 +267,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -86,16 +285,54 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF808080"/>
-      <name val="Menlo"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线 (Body)"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线 (Body)"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线 (Body)"/>
     </font>
   </fonts>
   <fills count="2">
@@ -121,8 +358,12 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -130,12 +371,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -451,8 +708,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF8CCF2-AE0D-0541-9EF1-0A620AC1EE56}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -460,27 +717,27 @@
     <col min="4" max="4" width="42.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="str">
         <f>CONCATENATE(A1,C1,B1)</f>
-        <v>常见XML 属性|描述</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+        <v>基本类型|大小(1个字节等于8位)</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
@@ -490,65 +747,311 @@
         <v>---|---</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
+    <row r="3" spans="1:4">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>0</v>
       </c>
       <c r="D3" t="str">
-        <f>CONCATENATE(A3,C3,B3)</f>
-        <v>android:iconifiedByDefault|是否自动缩小为图标</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+        <f t="shared" ref="D3:D38" si="0">CONCATENATE(A3,C3,B3)</f>
+        <v>-|-</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="18">
+      <c r="A4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>5</v>
       </c>
       <c r="C4" t="s">
         <v>0</v>
       </c>
       <c r="D4" t="str">
-        <f t="shared" ref="D4:D7" si="0">CONCATENATE(A4,C4,B4)</f>
-        <v>android:queryHint|提示文本</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>-27 = -128|27 -1 = 127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="37">
+      <c r="A5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="C5" t="s">
         <v>0</v>
       </c>
       <c r="D5" t="str">
         <f t="shared" si="0"/>
-        <v>|</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>\u0000' = Unicode 0|\uFFFF' = Unicode 216-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="18">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="C6" t="s">
         <v>0</v>
       </c>
       <c r="D6" t="str">
         <f t="shared" si="0"/>
-        <v>|</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+        <v>-215| 215-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="18">
+      <c r="A7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="C7" t="s">
         <v>0</v>
       </c>
       <c r="D7" t="str">
         <f t="shared" si="0"/>
-        <v>|</v>
+        <v>-231| 231-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18">
+      <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="str">
+        <f t="shared" si="0"/>
+        <v>-263 263-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v>IEEE754IEEE754</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="str">
+        <f t="shared" si="0"/>
+        <v>IEEE754IEEE754</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" t="str">
+        <f t="shared" si="0"/>
+        <v>--</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" t="str">
+        <f t="shared" si="0"/>
+        <v>--</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" si="0"/>
+        <v>--</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" t="str">
+        <f t="shared" si="0"/>
+        <v>--</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="D15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="D16" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="4:4">
+      <c r="D19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="4:4">
+      <c r="D20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="4:4">
+      <c r="D21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="4:4">
+      <c r="D23" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="4:4">
+      <c r="D24" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="4:4">
+      <c r="D25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="4:4">
+      <c r="D26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="4:4">
+      <c r="D27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="4:4">
+      <c r="D28" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="4:4">
+      <c r="D29" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="4:4">
+      <c r="D30" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="4:4">
+      <c r="D31" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="4:4">
+      <c r="D32" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="4:4">
+      <c r="D33" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="4:4">
+      <c r="D34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="4:4">
+      <c r="D35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="4:4">
+      <c r="D36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="4:4">
+      <c r="D37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="4:4">
+      <c r="D38" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -556,15 +1059,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFAE3BDA-4580-6A46-AC63-A44DE16870BF}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{C22551F7-B758-DF45-BF22-022C93C8FDFB}"/>
   </hyperlinks>

--- a/tools/convert_excel_to_md_model.xlsx
+++ b/tools/convert_excel_to_md_model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/project/YingVickyCao.github.io/tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9704B0-0080-0047-B514-09F4DEA06597}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6AA481-081F-EF46-B2E6-E2FD5B3062D8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{CE9A8E0E-7C5D-A34E-B819-2211D9A6DAA1}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="17540" xr2:uid="{CE9A8E0E-7C5D-A34E-B819-2211D9A6DAA1}"/>
   </bookViews>
   <sheets>
     <sheet name="xml" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>|</t>
   </si>
@@ -46,50 +46,115 @@
   </si>
   <si>
     <t>-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>模版方法</t>
-  </si>
-  <si>
-    <t>策略</t>
-  </si>
-  <si>
-    <t>定义一个算法家族，并让这些算法可以互换。因为每个算法都被封装起来， 所以客户可以轻易地使用不同的算法</t>
-  </si>
-  <si>
-    <t>算法结构保持不变，子类对算法中的个别步骤可以有不同的实现细节</t>
-  </si>
-  <si>
-    <t>使用继承进行算法的实现</t>
-  </si>
-  <si>
-    <t>通过对象组合的方式，让客户可以选择算法实现</t>
-  </si>
-  <si>
-    <t>代码重用：相同的代码放到超类中</t>
-  </si>
-  <si>
-    <t>因为使用对象组合，所以更有弹性。客户可以在运行时通过使用不同的策略对象从而改变算法。</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>创建框架时，很有用</t>
-  </si>
-  <si>
-    <t>依赖超类中的方法的实现，这是算法中的一部分</t>
-  </si>
-  <si>
-    <t>不依赖任何人，整个算法自己搞定</t>
+  </si>
+  <si>
+    <t>First supported API level</t>
+  </si>
+  <si>
+    <t>Canvas</t>
+  </si>
+  <si>
+    <t>drawBitmapMesh() (colors array)</t>
+  </si>
+  <si>
+    <t>drawPicture()</t>
+  </si>
+  <si>
+    <t>drawPosText()</t>
+  </si>
+  <si>
+    <t>drawTextOnPath()</t>
+  </si>
+  <si>
+    <t>drawVertices()</t>
+  </si>
+  <si>
+    <t>✗</t>
+  </si>
+  <si>
+    <t>setDrawFilter()</t>
+  </si>
+  <si>
+    <t>clipPath()</t>
+  </si>
+  <si>
+    <t>clipRegion()</t>
+  </si>
+  <si>
+    <t>clipRect(Region.Op.XOR)</t>
+  </si>
+  <si>
+    <t>clipRect(Region.Op.Difference)</t>
+  </si>
+  <si>
+    <t>clipRect(Region.Op.ReverseDifference)</t>
+  </si>
+  <si>
+    <t>clipRect() with rotation/perspective</t>
+  </si>
+  <si>
+    <t>Paint</t>
+  </si>
+  <si>
+    <t>setAntiAlias() (for text)</t>
+  </si>
+  <si>
+    <t>setAntiAlias() (for lines)</t>
+  </si>
+  <si>
+    <t>setFilterBitmap()</t>
+  </si>
+  <si>
+    <t>setLinearText()</t>
+  </si>
+  <si>
+    <t>setMaskFilter()</t>
+  </si>
+  <si>
+    <t>setPathEffect() (for lines)</t>
+  </si>
+  <si>
+    <t>setShadowLayer() (other than text)</t>
+  </si>
+  <si>
+    <t>setStrokeCap() (for lines)</t>
+  </si>
+  <si>
+    <t>setStrokeCap() (for points)</t>
+  </si>
+  <si>
+    <t>setSubpixelText()</t>
+  </si>
+  <si>
+    <t>Xfermode</t>
+  </si>
+  <si>
+    <t>PorterDuff.Mode.DARKEN (framebuffer)</t>
+  </si>
+  <si>
+    <t>PorterDuff.Mode.LIGHTEN (framebuffer)</t>
+  </si>
+  <si>
+    <t>PorterDuff.Mode.OVERLAY (framebuffer)</t>
+  </si>
+  <si>
+    <t>Shader</t>
+  </si>
+  <si>
+    <t>ComposeShader inside ComposeShader</t>
+  </si>
+  <si>
+    <t>Same type shaders inside ComposeShader</t>
+  </si>
+  <si>
+    <t>Local matrix on ComposeShader</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -109,23 +174,6 @@
       <sz val="9"/>
       <name val="Calibri"/>
       <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -166,12 +214,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -511,330 +556,457 @@
   <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="55.1640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="73.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="42.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="3"/>
+    <col min="1" max="1" width="55.1640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="73.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="42.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="2" t="str">
         <f>CONCATENATE(A1,C1,B1)</f>
-        <v>模版方法|策略</v>
+        <v>-|First supported API level</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="2" t="str">
         <f>CONCATENATE(A2,C2,B2)</f>
         <v>---|---</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="str">
+        <f t="shared" ref="D3:D38" si="0">CONCATENATE(A3,C3,B3)</f>
+        <v>-|First supported API level</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Canvas|</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <f>CONCATENATE(A5,C5,B6)</f>
+        <v>drawBitmapMesh() (colors array)|23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B6" s="6">
+        <v>23</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="str">
-        <f t="shared" ref="D3:D38" si="0">CONCATENATE(A3,C3,B3)</f>
-        <v>算法结构保持不变，子类对算法中的个别步骤可以有不同的实现细节|定义一个算法家族，并让这些算法可以互换。因为每个算法都被封装起来， 所以客户可以轻易地使用不同的算法</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>使用继承进行算法的实现|通过对象组合的方式，让客户可以选择算法实现</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="str">
-        <f>CONCATENATE(A5,C5,B6)</f>
-        <v>代码重用：相同的代码放到超类中|因为使用对象组合，所以更有弹性。客户可以在运行时通过使用不同的策略对象从而改变算法。</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" s="5"/>
-      <c r="B6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="e">
+      <c r="D6" s="2" t="e">
         <f>CONCATENATE(A6,C6,#REF!)</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="7">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>drawPosText()|16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="7">
+        <v>16</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>drawTextOnPath()16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>drawVertices()✗</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="8">
+        <v>16</v>
+      </c>
+      <c r="D10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>setDrawFilter()16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>创建框架时，很有用|</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="B11" s="7">
+        <v>18</v>
+      </c>
+      <c r="D11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>clipPath()18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B12" s="7">
+        <v>18</v>
+      </c>
+      <c r="D12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>clipRegion()18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>依赖超类中的方法的实现，这是算法中的一部分不依赖任何人，整个算法自己搞定</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="D9" s="3" t="str">
+      <c r="B13" s="7">
+        <v>18</v>
+      </c>
+      <c r="D13" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>clipRect(Region.Op.XOR)18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="7">
+        <v>18</v>
+      </c>
+      <c r="D14" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>clipRect(Region.Op.Difference)18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>18</v>
+      </c>
+      <c r="D15" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>clipRect(Region.Op.ReverseDifference)18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2">
+        <v>18</v>
+      </c>
+      <c r="D16" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>clipRect() with rotation/perspective18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Paint</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="2">
+        <v>18</v>
+      </c>
+      <c r="D18" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>setAntiAlias() (for text)18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="2">
+        <v>16</v>
+      </c>
+      <c r="D19" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>setAntiAlias() (for lines)16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="2">
+        <v>17</v>
+      </c>
+      <c r="D20" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>setFilterBitmap()17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>setLinearText()✗</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>setMaskFilter()✗</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="2">
+        <v>28</v>
+      </c>
+      <c r="D23" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>setPathEffect() (for lines)28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="2">
+        <v>28</v>
+      </c>
+      <c r="D24" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>setShadowLayer() (other than text)28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="2">
+        <v>18</v>
+      </c>
+      <c r="D25" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>setStrokeCap() (for lines)18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="2">
+        <v>19</v>
+      </c>
+      <c r="D26" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>setStrokeCap() (for points)19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="2">
+        <v>28</v>
+      </c>
+      <c r="D27" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>setSubpixelText()28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Xfermode</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="2">
+        <v>28</v>
+      </c>
+      <c r="D29" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>PorterDuff.Mode.DARKEN (framebuffer)28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="2">
+        <v>28</v>
+      </c>
+      <c r="D30" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>PorterDuff.Mode.LIGHTEN (framebuffer)28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="2">
+        <v>28</v>
+      </c>
+      <c r="D31" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>PorterDuff.Mode.OVERLAY (framebuffer)28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Shader</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="2">
+        <v>28</v>
+      </c>
+      <c r="D33" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>ComposeShader inside ComposeShader28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="2">
+        <v>28</v>
+      </c>
+      <c r="D34" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Same type shaders inside ComposeShader28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="2">
+        <v>18</v>
+      </c>
+      <c r="D35" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Local matrix on ComposeShader18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D36" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="D10" s="3" t="str">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D37" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>--</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>--</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>--</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>--</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D15" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D16" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D17" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D18" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D19" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D20" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D21" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D22" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D23" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D24" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D25" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D26" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D27" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D28" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D29" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D30" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D31" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D32" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D33" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D34" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D35" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D36" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D37" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D38" s="3" t="str">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D38" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>

--- a/tools/convert_excel_to_md_model.xlsx
+++ b/tools/convert_excel_to_md_model.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/project/YingVickyCao.github.io/tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6AA481-081F-EF46-B2E6-E2FD5B3062D8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C07DDFE9-A407-9241-BD74-2E8EC9C08EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="17540" xr2:uid="{CE9A8E0E-7C5D-A34E-B819-2211D9A6DAA1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t>|</t>
   </si>
@@ -51,103 +51,142 @@
     <t>First supported API level</t>
   </si>
   <si>
-    <t>Canvas</t>
-  </si>
-  <si>
-    <t>drawBitmapMesh() (colors array)</t>
-  </si>
-  <si>
-    <t>drawPicture()</t>
-  </si>
-  <si>
-    <t>drawPosText()</t>
-  </si>
-  <si>
-    <t>drawTextOnPath()</t>
-  </si>
-  <si>
-    <t>drawVertices()</t>
-  </si>
-  <si>
-    <t>✗</t>
-  </si>
-  <si>
-    <t>setDrawFilter()</t>
-  </si>
-  <si>
-    <t>clipPath()</t>
-  </si>
-  <si>
-    <t>clipRegion()</t>
-  </si>
-  <si>
-    <t>clipRect(Region.Op.XOR)</t>
-  </si>
-  <si>
-    <t>clipRect(Region.Op.Difference)</t>
-  </si>
-  <si>
-    <t>clipRect(Region.Op.ReverseDifference)</t>
-  </si>
-  <si>
-    <t>clipRect() with rotation/perspective</t>
-  </si>
-  <si>
-    <t>Paint</t>
-  </si>
-  <si>
-    <t>setAntiAlias() (for text)</t>
-  </si>
-  <si>
-    <t>setAntiAlias() (for lines)</t>
-  </si>
-  <si>
-    <t>setFilterBitmap()</t>
-  </si>
-  <si>
-    <t>setLinearText()</t>
-  </si>
-  <si>
-    <t>setMaskFilter()</t>
-  </si>
-  <si>
-    <t>setPathEffect() (for lines)</t>
-  </si>
-  <si>
-    <t>setShadowLayer() (other than text)</t>
-  </si>
-  <si>
-    <t>setStrokeCap() (for lines)</t>
-  </si>
-  <si>
-    <t>setStrokeCap() (for points)</t>
-  </si>
-  <si>
-    <t>setSubpixelText()</t>
-  </si>
-  <si>
-    <t>Xfermode</t>
-  </si>
-  <si>
-    <t>PorterDuff.Mode.DARKEN (framebuffer)</t>
-  </si>
-  <si>
-    <t>PorterDuff.Mode.LIGHTEN (framebuffer)</t>
-  </si>
-  <si>
-    <t>PorterDuff.Mode.OVERLAY (framebuffer)</t>
-  </si>
-  <si>
-    <t>Shader</t>
-  </si>
-  <si>
-    <t>ComposeShader inside ComposeShader</t>
-  </si>
-  <si>
-    <t>Same type shaders inside ComposeShader</t>
-  </si>
-  <si>
-    <t>Local matrix on ComposeShader</t>
+    <t>通配符</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>%@</t>
+  </si>
+  <si>
+    <t>对象</t>
+  </si>
+  <si>
+    <t>%d,%i</t>
+  </si>
+  <si>
+    <t>整型 (%i的老写法)</t>
+  </si>
+  <si>
+    <t>%hd</t>
+  </si>
+  <si>
+    <t>短整型</t>
+  </si>
+  <si>
+    <t>%ld,%lld</t>
+  </si>
+  <si>
+    <t>长整型</t>
+  </si>
+  <si>
+    <t>%u</t>
+  </si>
+  <si>
+    <t>无符整型</t>
+  </si>
+  <si>
+    <t>%f</t>
+  </si>
+  <si>
+    <t>浮点型和double型</t>
+  </si>
+  <si>
+    <t>%0.2f</t>
+  </si>
+  <si>
+    <t>精度浮点数，只保留两位小数</t>
+  </si>
+  <si>
+    <t>%x:</t>
+  </si>
+  <si>
+    <t>为32位的无符号整型数(unsigned int),打印使用数字0-9的十六进制,小写a-f;</t>
+  </si>
+  <si>
+    <t>%X:</t>
+  </si>
+  <si>
+    <t>为32位的无符号整型数(unsigned int),打印使用数字0-9的十六进制,大写A-F;</t>
+  </si>
+  <si>
+    <t>%o</t>
+  </si>
+  <si>
+    <t>八进制</t>
+  </si>
+  <si>
+    <t>%zu</t>
+  </si>
+  <si>
+    <t>size_t</t>
+  </si>
+  <si>
+    <t>%p</t>
+  </si>
+  <si>
+    <t>指针地址</t>
+  </si>
+  <si>
+    <t>%e</t>
+  </si>
+  <si>
+    <t>float/double （科学计算）</t>
+  </si>
+  <si>
+    <t>%g</t>
+  </si>
+  <si>
+    <t>float/double （科学技术法）</t>
+  </si>
+  <si>
+    <t>%s</t>
+  </si>
+  <si>
+    <t>char * 字符串</t>
+  </si>
+  <si>
+    <t>%.*s</t>
+  </si>
+  <si>
+    <t>Pascal字符串</t>
+  </si>
+  <si>
+    <t>%c</t>
+  </si>
+  <si>
+    <t>char 字符</t>
+  </si>
+  <si>
+    <t>%C</t>
+  </si>
+  <si>
+    <t>unichar</t>
+  </si>
+  <si>
+    <t>%Lf</t>
+  </si>
+  <si>
+    <t>64位double</t>
+  </si>
+  <si>
+    <t>%lu</t>
+  </si>
+  <si>
+    <t>sizeof(i)内存中所占字节数</t>
+  </si>
+  <si>
+    <t>CGRect</t>
+  </si>
+  <si>
+    <t>NSLog(@”%@”,NSStringFromCGRect(someCGRect)); 或者CFShow(NSStringFromCGRect(someCGRect));CFShow能打印地址.</t>
+  </si>
+  <si>
+    <t>CGSize</t>
+  </si>
+  <si>
+    <t>NSLog(@”%@”,NSStringFromCGSize(someCG Size ));</t>
   </si>
 </sst>
 </file>
@@ -565,17 +604,17 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="str">
         <f>CONCATENATE(A1,C1,B1)</f>
-        <v>-|First supported API level</v>
+        <v>通配符|描述</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -612,36 +651,38 @@
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Canvas|</v>
+        <v>通配符|描述</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2">
-        <v>18</v>
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="2" t="str">
         <f>CONCATENATE(A5,C5,B6)</f>
-        <v>drawBitmapMesh() (colors array)|23</v>
+        <v>%@|整型 (%i的老写法)</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="6">
-        <v>23</v>
+        <v>9</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>0</v>
@@ -653,359 +694,314 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="7">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D7" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>drawPosText()|16</v>
+        <v>%hd|短整型</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="D8" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>drawTextOnPath()16</v>
+        <v>%ld,%lld长整型</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>drawVertices()✗</v>
+        <v>%u无符整型</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="8">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="D10" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>setDrawFilter()16</v>
+        <v>%f浮点型和double型</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="7">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D11" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>clipPath()18</v>
+        <v>%0.2f精度浮点数，只保留两位小数</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="7">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D12" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>clipRegion()18</v>
+        <v>%x:为32位的无符号整型数(unsigned int),打印使用数字0-9的十六进制,小写a-f;</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="7">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="D13" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>clipRect(Region.Op.XOR)18</v>
+        <v>%X:为32位的无符号整型数(unsigned int),打印使用数字0-9的十六进制,大写A-F;</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="7">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="D14" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>clipRect(Region.Op.Difference)18</v>
+        <v>%o八进制</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="2">
-        <v>18</v>
+        <v>27</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="D15" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>clipRect(Region.Op.ReverseDifference)18</v>
+        <v>%zusize_t</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="2">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="D16" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>clipRect() with rotation/perspective18</v>
+        <v>%p指针地址</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="D17" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Paint</v>
+        <v>%efloat/double （科学计算）</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="2">
-        <v>18</v>
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="D18" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>setAntiAlias() (for text)18</v>
+        <v>%gfloat/double （科学技术法）</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="2">
-        <v>16</v>
+        <v>35</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="D19" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>setAntiAlias() (for lines)16</v>
+        <v>%schar * 字符串</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="2">
-        <v>17</v>
+        <v>37</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="D20" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>setFilterBitmap()17</v>
+        <v>%.*sPascal字符串</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D21" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>setLinearText()✗</v>
+        <v>%cchar 字符</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="D22" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>setMaskFilter()✗</v>
+        <v>%Cunichar</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="2">
-        <v>28</v>
+        <v>43</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="D23" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>setPathEffect() (for lines)28</v>
+        <v>%Lf64位double</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="2">
-        <v>28</v>
+        <v>45</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="D24" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>setShadowLayer() (other than text)28</v>
+        <v>%lusizeof(i)内存中所占字节数</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="2">
-        <v>18</v>
+        <v>47</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="D25" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>setStrokeCap() (for lines)18</v>
+        <v>CGRectNSLog(@”%@”,NSStringFromCGRect(someCGRect)); 或者CFShow(NSStringFromCGRect(someCGRect));CFShow能打印地址.</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="2">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="D26" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>setStrokeCap() (for points)19</v>
+        <v>CGSizeNSLog(@”%@”,NSStringFromCGSize(someCG Size ));</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="2">
-        <v>28</v>
-      </c>
       <c r="D27" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>setSubpixelText()28</v>
+        <v/>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="D28" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Xfermode</v>
+        <v/>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="2">
-        <v>28</v>
-      </c>
       <c r="D29" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>PorterDuff.Mode.DARKEN (framebuffer)28</v>
+        <v/>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="2">
-        <v>28</v>
-      </c>
       <c r="D30" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>PorterDuff.Mode.LIGHTEN (framebuffer)28</v>
+        <v/>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="2">
-        <v>28</v>
-      </c>
       <c r="D31" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>PorterDuff.Mode.OVERLAY (framebuffer)28</v>
+        <v/>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="D32" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Shader</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="2">
-        <v>28</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D33" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>ComposeShader inside ComposeShader28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="2">
-        <v>28</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D34" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Same type shaders inside ComposeShader28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="2">
-        <v>18</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D35" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Local matrix on ComposeShader18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D36" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D37" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D38" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
